--- a/mosip_master/xlsx/blocklisted_words.xlsx
+++ b/mosip_master/xlsx/blocklisted_words.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t xml:space="preserve">lang_code</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">fool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">useless</t>
   </si>
   <si>
     <t xml:space="preserve">dammit</t>
@@ -78,7 +81,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -107,12 +110,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,11 +178,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -206,7 +203,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.4296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.28"/>
@@ -285,29 +282,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>13</v>
-      </c>
       <c r="C7" s="0" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -315,15 +312,29 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
